--- a/test-case-quan-ly-tuyen-dung-project.xlsx
+++ b/test-case-quan-ly-tuyen-dung-project.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThu\QuanLyTuyenDungProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{354D94B0-3C91-4312-9643-922D52994218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581AE48A-71F4-4344-A1A2-849CBCB1D761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="821" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="90">
   <si>
     <t>31/07/2007</t>
   </si>
@@ -484,12 +484,43 @@
     <t>Admin được đăng tin</t>
   </si>
   <si>
+    <t>Tin tạo thành công, chuyển về trang chủ, tin xuất hiện trong danh sách.</t>
+  </si>
+  <si>
+    <t>TC2.3</t>
+  </si>
+  <si>
+    <t>Chưa đăng nhập không được đăng tin</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Không đăng nhập. 2. Truy cập trực tiếp URL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <color rgb="FFD1D5DA"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="163"/>
+      </rPr>
+      <t>/jobs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD1D5DA"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
     <t>1. Đăng nhập Admin. 
 2. Điền đầy đủ thông tin hợp lệ.
-3. Nhấn "Đăng".</t>
-  </si>
-  <si>
-    <t>Tin tạo thành công, chuyển về trang chủ, tin xuất hiện trong danh sách.</t>
+3. Nhấn "XÁC NHẬN ĐĂNG TIN".</t>
   </si>
 </sst>
 </file>
@@ -500,7 +531,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -657,6 +688,20 @@
       <family val="2"/>
       <charset val="163"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFD1D5DA"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <color rgb="FFD1D5DA"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="163"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1172,7 +1217,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1456,6 +1501,51 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1468,9 +1558,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1499,12 +1586,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1531,47 +1612,14 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2042,11 +2090,11 @@
       <c r="B6" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="116" t="s">
+      <c r="C6" s="130" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="116"/>
-      <c r="E6" s="117"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="131"/>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
     </row>
@@ -2055,11 +2103,11 @@
       <c r="B7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="116" t="s">
+      <c r="C7" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="116"/>
-      <c r="E7" s="117"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="131"/>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
     </row>
@@ -2288,9 +2336,9 @@
       <c r="A1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
@@ -2302,9 +2350,9 @@
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A2" s="7"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -2318,54 +2366,54 @@
       <c r="A3" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="116" t="s">
+      <c r="B3" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="117"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="131"/>
       <c r="E3" s="66"/>
       <c r="F3" s="66"/>
       <c r="G3" s="66"/>
       <c r="H3" s="66"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="118"/>
-      <c r="K3" s="118"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="132"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="12.75">
       <c r="A4" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="119" t="s">
+      <c r="B4" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="120"/>
-      <c r="D4" s="121"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135"/>
       <c r="E4" s="66"/>
       <c r="F4" s="66"/>
       <c r="G4" s="66"/>
       <c r="H4" s="66"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="132"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:12" s="77" customFormat="1" ht="12.75">
       <c r="A5" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="109" t="s">
+      <c r="B5" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="111"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="112"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="112"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
@@ -2387,9 +2435,9 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="118"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="132"/>
       <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
@@ -2411,16 +2459,16 @@
       <c r="F7" s="67"/>
       <c r="G7" s="67"/>
       <c r="H7" s="67"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
       <c r="L7" s="9"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="122"/>
-      <c r="B8" s="122"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
+      <c r="A8" s="136"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="136"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -2431,31 +2479,31 @@
       <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" s="79" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="126" t="s">
+      <c r="B9" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="124" t="s">
+      <c r="C9" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="127" t="s">
+      <c r="D9" s="139" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="133" t="s">
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="141"/>
+      <c r="H9" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="123" t="s">
+      <c r="I9" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="123" t="s">
+      <c r="J9" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="123" t="s">
+      <c r="K9" s="110" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="78"/>
@@ -2464,43 +2512,43 @@
       <c r="A10" s="146"/>
       <c r="B10" s="147"/>
       <c r="C10" s="146"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="124"/>
-      <c r="K10" s="124"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="111"/>
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" s="80" customFormat="1" ht="15">
-      <c r="A11" s="138"/>
-      <c r="B11" s="138"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="138"/>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
-      <c r="J11" s="138"/>
-      <c r="K11" s="139"/>
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="117"/>
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" ht="12.75">
-      <c r="A12" s="140" t="s">
+      <c r="A12" s="118" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="141"/>
-      <c r="C12" s="141"/>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="141"/>
-      <c r="I12" s="141"/>
-      <c r="J12" s="141"/>
-      <c r="K12" s="142"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="120"/>
     </row>
     <row r="13" spans="1:12" s="4" customFormat="1" ht="76.5" outlineLevel="1">
       <c r="A13" s="84" t="s">
@@ -2512,11 +2560,11 @@
       <c r="C13" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="143" t="s">
+      <c r="D13" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
       <c r="G13" s="82"/>
       <c r="H13" s="101"/>
       <c r="I13" s="96"/>
@@ -2526,11 +2574,11 @@
       <c r="K13" s="81"/>
     </row>
     <row r="14" spans="1:12" s="4" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A14" s="134" t="s">
+      <c r="A14" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="135"/>
-      <c r="C14" s="135"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
       <c r="D14" s="94"/>
       <c r="E14" s="94"/>
       <c r="F14" s="94"/>
@@ -2550,11 +2598,11 @@
       <c r="C15" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="136" t="s">
+      <c r="D15" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
       <c r="G15" s="82"/>
       <c r="H15" s="101"/>
       <c r="I15" s="91"/>
@@ -2564,11 +2612,11 @@
       <c r="K15" s="81"/>
     </row>
     <row r="16" spans="1:12" s="4" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A16" s="134" t="s">
+      <c r="A16" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135"/>
+      <c r="B16" s="113"/>
+      <c r="C16" s="113"/>
       <c r="D16" s="94"/>
       <c r="E16" s="94"/>
       <c r="F16" s="94"/>
@@ -2588,11 +2636,11 @@
       <c r="C17" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="136" t="s">
+      <c r="D17" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
       <c r="G17" s="82"/>
       <c r="H17" s="101"/>
       <c r="I17" s="91"/>
@@ -2641,6 +2689,15 @@
     <row r="55" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="B5:D5"/>
@@ -2657,15 +2714,6 @@
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="A14:C14"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2679,7 +2727,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -2697,9 +2745,9 @@
       <c r="A1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
@@ -2711,9 +2759,9 @@
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A2" s="7"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -2727,54 +2775,54 @@
       <c r="A3" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="116" t="s">
+      <c r="B3" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="117"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="131"/>
       <c r="E3" s="66"/>
       <c r="F3" s="66"/>
       <c r="G3" s="66"/>
       <c r="H3" s="66"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="118"/>
-      <c r="K3" s="118"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="132"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="12.75">
       <c r="A4" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="119" t="s">
+      <c r="B4" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="120"/>
-      <c r="D4" s="121"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135"/>
       <c r="E4" s="66"/>
       <c r="F4" s="66"/>
       <c r="G4" s="66"/>
       <c r="H4" s="66"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="132"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:12" s="77" customFormat="1" ht="12.75">
       <c r="A5" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="109" t="s">
+      <c r="B5" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="111"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="112"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="112"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
@@ -2782,23 +2830,23 @@
         <v>40</v>
       </c>
       <c r="B6" s="88">
-        <f>COUNTIF(J12:J18,"Pass")</f>
+        <f>COUNTIF(J12:J19,"Pass")</f>
         <v>4</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="13">
-        <f>COUNTIF(J10:J737,"Pending")</f>
+        <f>COUNTIF(J10:J738,"Pending")</f>
         <v>0</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="118"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="132"/>
       <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
@@ -2806,30 +2854,30 @@
         <v>6</v>
       </c>
       <c r="B7" s="89">
-        <f>COUNTIF(J12:J18,"Fail")</f>
+        <f>COUNTIF(J12:J19,"Fail")</f>
         <v>0</v>
       </c>
       <c r="C7" s="29" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="64">
-        <f>COUNTA(A12:A18) -15</f>
-        <v>-8</v>
+        <f>COUNTA(A12:A19) -15</f>
+        <v>-7</v>
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="67"/>
       <c r="G7" s="67"/>
       <c r="H7" s="67"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
       <c r="L7" s="9"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="122"/>
-      <c r="B8" s="122"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
+      <c r="A8" s="136"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="136"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -2840,76 +2888,76 @@
       <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" s="79" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="123" t="s">
+      <c r="A9" s="110" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="137" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="123" t="s">
+      <c r="C9" s="110" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="127" t="s">
+      <c r="D9" s="139" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="133" t="s">
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="141"/>
+      <c r="H9" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="123" t="s">
+      <c r="I9" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="J9" s="123" t="s">
+      <c r="J9" s="110" t="s">
         <v>73</v>
       </c>
-      <c r="K9" s="123" t="s">
+      <c r="K9" s="110" t="s">
         <v>74</v>
       </c>
       <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="124"/>
-      <c r="B10" s="126"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="124"/>
-      <c r="K10" s="124"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="111"/>
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" s="80" customFormat="1" ht="15">
-      <c r="A11" s="138"/>
-      <c r="B11" s="138"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="138"/>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
-      <c r="J11" s="138"/>
-      <c r="K11" s="139"/>
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="117"/>
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" ht="12.75">
-      <c r="A12" s="140" t="e" vm="1">
+      <c r="A12" s="118" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B12" s="141"/>
-      <c r="C12" s="141"/>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="141"/>
-      <c r="I12" s="141"/>
-      <c r="J12" s="141"/>
-      <c r="K12" s="142"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="120"/>
     </row>
     <row r="13" spans="1:12" s="4" customFormat="1" ht="114.75" outlineLevel="1">
       <c r="A13" s="84" t="s">
@@ -2921,11 +2969,11 @@
       <c r="C13" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="143" t="s">
+      <c r="D13" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
       <c r="G13" s="82"/>
       <c r="H13" s="101" t="e" vm="2">
         <v>#VALUE!</v>
@@ -2939,11 +2987,11 @@
       <c r="K13" s="81"/>
     </row>
     <row r="14" spans="1:12" s="4" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="141"/>
-      <c r="C14" s="141"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="119"/>
       <c r="D14" s="94"/>
       <c r="E14" s="94"/>
       <c r="F14" s="94"/>
@@ -2963,11 +3011,11 @@
       <c r="C15" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="145" t="s">
+      <c r="D15" s="123" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
       <c r="G15" s="82"/>
       <c r="H15" s="101" t="e" vm="3">
         <v>#VALUE!</v>
@@ -2988,13 +3036,13 @@
         <v>84</v>
       </c>
       <c r="C16" s="105" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="148" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="113" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
       <c r="G16" s="108"/>
       <c r="H16" s="108" t="e" vm="4">
         <v>#VALUE!</v>
@@ -3007,47 +3055,65 @@
       </c>
       <c r="K16" s="107"/>
     </row>
-    <row r="17" spans="1:11" s="4" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A17" s="134" t="s">
+    <row r="17" spans="1:11" s="4" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+      <c r="A17" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="92" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="109"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="107"/>
+    </row>
+    <row r="18" spans="1:11" s="4" customFormat="1" ht="12.75" outlineLevel="1">
+      <c r="A18" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="135"/>
-      <c r="C17" s="135"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="95"/>
-    </row>
-    <row r="18" spans="1:11" s="4" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
-      <c r="A18" s="84" t="s">
+      <c r="B18" s="113"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="95"/>
+    </row>
+    <row r="19" spans="1:11" s="4" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+      <c r="A19" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="102" t="s">
+      <c r="B19" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="83" t="s">
+      <c r="C19" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="136" t="s">
+      <c r="D19" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="137"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="101" t="e" vm="5">
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="82"/>
+      <c r="H19" s="101" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="I18" s="91"/>
-      <c r="J18" s="83" t="s">
+      <c r="I19" s="91"/>
+      <c r="J19" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="K18" s="81"/>
-    </row>
-    <row r="19" spans="1:11" ht="12" customHeight="1"/>
+      <c r="K19" s="81"/>
+    </row>
     <row r="20" spans="1:11" ht="12" customHeight="1"/>
     <row r="21" spans="1:11" ht="12" customHeight="1"/>
     <row r="22" spans="1:11" ht="12" customHeight="1"/>
@@ -3085,18 +3151,9 @@
     <row r="54" ht="12" customHeight="1"/>
     <row r="55" ht="12" customHeight="1"/>
     <row r="56" ht="12" customHeight="1"/>
+    <row r="57" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D15:F15"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="D16:F16"/>
@@ -3113,6 +3170,16 @@
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:G10"/>
     <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/test-case-quan-ly-tuyen-dung-project.xlsx
+++ b/test-case-quan-ly-tuyen-dung-project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThu\QuanLyTuyenDungProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581AE48A-71F4-4344-A1A2-849CBCB1D761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199E27C7-FA73-4641-9B72-BDD2B5C366D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="821" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,34 +493,13 @@
     <t>Chưa đăng nhập không được đăng tin</t>
   </si>
   <si>
-    <r>
-      <t>1. Không đăng nhập. 2. Truy cập trực tiếp URL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <color rgb="FFD1D5DA"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>/jobs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFD1D5DA"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="163"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>1. Đăng nhập Admin. 
 2. Điền đầy đủ thông tin hợp lệ.
 3. Nhấn "XÁC NHẬN ĐĂNG TIN".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Không đăng nhập. 
+2.  Nhấn vào "menu tài khoản người dùng" -&gt; Nhấn "Đăng tin tuyển dụng". </t>
   </si>
 </sst>
 </file>
@@ -531,7 +510,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -686,20 +665,6 @@
       <color rgb="FFFF0000"/>
       <name val="Tahoma"/>
       <family val="2"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFD1D5DA"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <sz val="9.9"/>
-      <color rgb="FFD1D5DA"/>
-      <name val="Courier New"/>
-      <family val="3"/>
       <charset val="163"/>
     </font>
   </fonts>
@@ -3036,7 +3001,7 @@
         <v>84</v>
       </c>
       <c r="C16" s="105" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" s="148" t="s">
         <v>85</v>
@@ -3063,7 +3028,7 @@
         <v>87</v>
       </c>
       <c r="C17" s="105" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D17" s="109"/>
       <c r="E17" s="109"/>

--- a/test-case-quan-ly-tuyen-dung-project.xlsx
+++ b/test-case-quan-ly-tuyen-dung-project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThu\QuanLyTuyenDungProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199E27C7-FA73-4641-9B72-BDD2B5C366D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77C90FC3-1A22-4721-9917-CF75CD769D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="821" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-4812" windowWidth="30936" windowHeight="16896" tabRatio="821" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="97" r:id="rId1"/>
@@ -53,7 +53,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="7">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -89,8 +89,22 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="7">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -106,12 +120,18 @@
     <bk>
       <rc t="1" v="4"/>
     </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="106">
   <si>
     <t>31/07/2007</t>
   </si>
@@ -500,6 +520,64 @@
   <si>
     <t xml:space="preserve">1. Không đăng nhập. 
 2.  Nhấn vào "menu tài khoản người dùng" -&gt; Nhấn "Đăng tin tuyển dụng". </t>
+  </si>
+  <si>
+    <t>Nhóm 3 — Ràng buộc Tiêu đề</t>
+  </si>
+  <si>
+    <t>Nhóm 1 — Đăng tin hợp lệ</t>
+  </si>
+  <si>
+    <t>TC3.1</t>
+  </si>
+  <si>
+    <t>Tiêu đề bỏ trống</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập NTD. 
+2. Để trống Tiêu đề. 
+3. Điền các trường còn lại hợp lệ. 
+4. Nhấn "XÁC NHẬN ĐĂNG TIN".</t>
+  </si>
+  <si>
+    <t>Quay lại ô nhập tiêu đề và hiện thông báo không được bỏ trống</t>
+  </si>
+  <si>
+    <t>TC3.2</t>
+  </si>
+  <si>
+    <t>Tiêu đề 9 ký tự (dưới tối thiểu)</t>
+  </si>
+  <si>
+    <t>1. Tiêu đề: "Tuyển IT" (9 ký tự). 
+2. Điền các trường còn lại hợp lệ. 
+3. Nhấn "XÁC NHẬN ĐĂNG TIN".</t>
+  </si>
+  <si>
+    <t>Trình duyệt hiển thị "Please lengthen this text to 10 characters or more (you are currently using 9 characters)", form không gửi lên server, không lưu tin.</t>
+  </si>
+  <si>
+    <t>TC3.3</t>
+  </si>
+  <si>
+    <t>Tiêu đề 10 ký tự (hợp lệ tối thiểu)</t>
+  </si>
+  <si>
+    <t>1. Tiêu đề: "Tuyển IT 1" (10 ký tự). 
+2. Điền các trường còn lại hợp lệ. 
+3. Nhấn "XÁC NHẬN ĐĂNG TIN".</t>
+  </si>
+  <si>
+    <t>TC3.4</t>
+  </si>
+  <si>
+    <t>Tiêu đề 255 ký tự (hợp lệ tối đa)</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập NTD. 
+2. Tiêu đề: chuỗi 255 ký tự hợp lệ. 
+3. Điền các trường còn lại hợp lệ. 
+4. Nhấn "XÁC NHẬN ĐĂNG TIN".</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1260,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1466,14 +1544,125 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1483,108 +1672,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1660,7 +1747,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1679,6 +1766,14 @@
   </rv>
   <rv s="0">
     <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -1700,6 +1795,8 @@
   <rel r:id="rId3"/>
   <rel r:id="rId4"/>
   <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
 </richValueRels>
 </file>
 
@@ -2055,11 +2152,11 @@
       <c r="B6" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="130" t="s">
+      <c r="C6" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="130"/>
-      <c r="E6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="132"/>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
     </row>
@@ -2068,11 +2165,11 @@
       <c r="B7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="130" t="s">
+      <c r="C7" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="130"/>
-      <c r="E7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
     </row>
@@ -2301,9 +2398,9 @@
       <c r="A1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
@@ -2315,9 +2412,9 @@
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A2" s="7"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -2331,54 +2428,54 @@
       <c r="A3" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="132"/>
       <c r="E3" s="66"/>
       <c r="F3" s="66"/>
       <c r="G3" s="66"/>
       <c r="H3" s="66"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="12.75">
       <c r="A4" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="133" t="s">
+      <c r="B4" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="134"/>
-      <c r="D4" s="135"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="136"/>
       <c r="E4" s="66"/>
       <c r="F4" s="66"/>
       <c r="G4" s="66"/>
       <c r="H4" s="66"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:12" s="77" customFormat="1" ht="12.75">
       <c r="A5" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="124" t="s">
+      <c r="B5" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="125"/>
-      <c r="D5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="127"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
@@ -2400,9 +2497,9 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="132"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
       <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
@@ -2424,16 +2521,16 @@
       <c r="F7" s="67"/>
       <c r="G7" s="67"/>
       <c r="H7" s="67"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
       <c r="L7" s="9"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="136"/>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
+      <c r="A8" s="137"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -2444,76 +2541,76 @@
       <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" s="79" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="114" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="138" t="s">
+      <c r="B9" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="111" t="s">
+      <c r="C9" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="139" t="s">
+      <c r="D9" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="140"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="141"/>
-      <c r="H9" s="145" t="s">
+      <c r="E9" s="141"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="146" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="110" t="s">
+      <c r="I9" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="110" t="s">
+      <c r="J9" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="110" t="s">
+      <c r="K9" s="113" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="146"/>
-      <c r="B10" s="147"/>
-      <c r="C10" s="146"/>
-      <c r="D10" s="142"/>
-      <c r="E10" s="143"/>
-      <c r="F10" s="143"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
+      <c r="A10" s="147"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="147"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" s="80" customFormat="1" ht="15">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="117"/>
+      <c r="A11" s="119"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="120"/>
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" ht="12.75">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="119"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="120"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="121"/>
     </row>
     <row r="13" spans="1:12" s="4" customFormat="1" ht="76.5" outlineLevel="1">
       <c r="A13" s="84" t="s">
@@ -2525,11 +2622,11 @@
       <c r="C13" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="121" t="s">
+      <c r="D13" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="123"/>
       <c r="G13" s="82"/>
       <c r="H13" s="101"/>
       <c r="I13" s="96"/>
@@ -2539,11 +2636,11 @@
       <c r="K13" s="81"/>
     </row>
     <row r="14" spans="1:12" s="4" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A14" s="112" t="s">
+      <c r="A14" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="113"/>
-      <c r="C14" s="113"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
       <c r="D14" s="94"/>
       <c r="E14" s="94"/>
       <c r="F14" s="94"/>
@@ -2563,11 +2660,11 @@
       <c r="C15" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="114" t="s">
+      <c r="D15" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
+      <c r="E15" s="123"/>
+      <c r="F15" s="123"/>
       <c r="G15" s="82"/>
       <c r="H15" s="101"/>
       <c r="I15" s="91"/>
@@ -2577,11 +2674,11 @@
       <c r="K15" s="81"/>
     </row>
     <row r="16" spans="1:12" s="4" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A16" s="112" t="s">
+      <c r="A16" s="149" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="113"/>
-      <c r="C16" s="113"/>
+      <c r="B16" s="150"/>
+      <c r="C16" s="150"/>
       <c r="D16" s="94"/>
       <c r="E16" s="94"/>
       <c r="F16" s="94"/>
@@ -2601,11 +2698,11 @@
       <c r="C17" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="114" t="s">
+      <c r="D17" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
       <c r="G17" s="82"/>
       <c r="H17" s="101"/>
       <c r="I17" s="91"/>
@@ -2692,7 +2789,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -2710,9 +2807,9 @@
       <c r="A1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
@@ -2724,9 +2821,9 @@
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A2" s="7"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -2740,54 +2837,54 @@
       <c r="A3" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="132"/>
       <c r="E3" s="66"/>
       <c r="F3" s="66"/>
       <c r="G3" s="66"/>
       <c r="H3" s="66"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="12.75">
       <c r="A4" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="133" t="s">
+      <c r="B4" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="134"/>
-      <c r="D4" s="135"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="136"/>
       <c r="E4" s="66"/>
       <c r="F4" s="66"/>
       <c r="G4" s="66"/>
       <c r="H4" s="66"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:12" s="77" customFormat="1" ht="12.75">
       <c r="A5" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="124" t="s">
+      <c r="B5" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="125"/>
-      <c r="D5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="127"/>
       <c r="E5" s="75"/>
       <c r="F5" s="75"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
       <c r="L5" s="76"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
@@ -2802,16 +2899,16 @@
         <v>41</v>
       </c>
       <c r="D6" s="13">
-        <f>COUNTIF(J10:J738,"Pending")</f>
+        <f>COUNTIF(J10:J741,"Pending")</f>
         <v>0</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="132"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
       <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
@@ -2833,16 +2930,16 @@
       <c r="F7" s="67"/>
       <c r="G7" s="67"/>
       <c r="H7" s="67"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
       <c r="L7" s="9"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="136"/>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
+      <c r="A8" s="137"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -2853,76 +2950,76 @@
       <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" s="79" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="110" t="s">
+      <c r="A9" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="137" t="s">
+      <c r="B9" s="138" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="110" t="s">
+      <c r="C9" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="139" t="s">
+      <c r="D9" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="140"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="141"/>
-      <c r="H9" s="145" t="s">
+      <c r="E9" s="141"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="146" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="110" t="s">
+      <c r="I9" s="113" t="s">
         <v>72</v>
       </c>
-      <c r="J9" s="110" t="s">
+      <c r="J9" s="113" t="s">
         <v>73</v>
       </c>
-      <c r="K9" s="110" t="s">
+      <c r="K9" s="113" t="s">
         <v>74</v>
       </c>
       <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="138"/>
-      <c r="C10" s="111"/>
-      <c r="D10" s="142"/>
-      <c r="E10" s="143"/>
-      <c r="F10" s="143"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
+      <c r="A10" s="114"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" s="80" customFormat="1" ht="15">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="117"/>
+      <c r="A11" s="119"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="120"/>
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" ht="12.75">
-      <c r="A12" s="118" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B12" s="119"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="120"/>
+      <c r="A12" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="121"/>
     </row>
     <row r="13" spans="1:12" s="4" customFormat="1" ht="114.75" outlineLevel="1">
       <c r="A13" s="84" t="s">
@@ -2934,13 +3031,13 @@
       <c r="C13" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="121" t="s">
+      <c r="D13" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="123"/>
       <c r="G13" s="82"/>
-      <c r="H13" s="101" t="e" vm="2">
+      <c r="H13" s="101" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="I13" s="96" t="s">
@@ -2952,11 +3049,11 @@
       <c r="K13" s="81"/>
     </row>
     <row r="14" spans="1:12" s="4" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="115" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="119"/>
-      <c r="C14" s="119"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
       <c r="D14" s="94"/>
       <c r="E14" s="94"/>
       <c r="F14" s="94"/>
@@ -2976,13 +3073,13 @@
       <c r="C15" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="123" t="s">
+      <c r="D15" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
+      <c r="E15" s="123"/>
+      <c r="F15" s="123"/>
       <c r="G15" s="82"/>
-      <c r="H15" s="101" t="e" vm="3">
+      <c r="H15" s="101" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="I15" s="103" t="s">
@@ -3003,13 +3100,13 @@
       <c r="C16" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="148" t="s">
+      <c r="D16" s="112" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
       <c r="G16" s="108"/>
-      <c r="H16" s="108" t="e" vm="4">
+      <c r="H16" s="108" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="I16" s="106" t="s">
@@ -3024,15 +3121,15 @@
       <c r="A17" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="92" t="s">
+      <c r="B17" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="109"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="109"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="124"/>
       <c r="G17" s="108"/>
       <c r="H17" s="108"/>
       <c r="I17" s="106"/>
@@ -3040,11 +3137,11 @@
       <c r="K17" s="107"/>
     </row>
     <row r="18" spans="1:11" s="4" customFormat="1" ht="12.75" outlineLevel="1">
-      <c r="A18" s="112" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="113"/>
-      <c r="C18" s="113"/>
+      <c r="A18" s="115" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
       <c r="D18" s="94"/>
       <c r="E18" s="94"/>
       <c r="F18" s="94"/>
@@ -3055,33 +3152,107 @@
       <c r="K18" s="95"/>
     </row>
     <row r="19" spans="1:11" s="4" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
-      <c r="A19" s="84" t="s">
-        <v>5</v>
+      <c r="A19" s="110" t="s">
+        <v>92</v>
       </c>
       <c r="B19" s="102" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="83" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="114" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
+        <v>93</v>
+      </c>
+      <c r="C19" s="82" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="82"/>
-      <c r="H19" s="101" t="e" vm="5">
+      <c r="H19" s="101" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="I19" s="91"/>
+      <c r="I19" s="103" t="s">
+        <v>76</v>
+      </c>
       <c r="J19" s="83" t="s">
         <v>40</v>
       </c>
       <c r="K19" s="81"/>
     </row>
-    <row r="20" spans="1:11" ht="12" customHeight="1"/>
-    <row r="21" spans="1:11" ht="12" customHeight="1"/>
-    <row r="22" spans="1:11" ht="12" customHeight="1"/>
+    <row r="20" spans="1:11" s="4" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+      <c r="A20" s="84" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="102" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I20" s="109" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="83"/>
+      <c r="K20" s="81"/>
+    </row>
+    <row r="21" spans="1:11" s="4" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+      <c r="A21" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="83" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="112" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I21" s="109" t="s">
+        <v>76</v>
+      </c>
+      <c r="J21" s="83"/>
+      <c r="K21" s="81"/>
+    </row>
+    <row r="22" spans="1:11" s="4" customFormat="1" ht="63.75" customHeight="1" outlineLevel="1">
+      <c r="A22" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="83" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="112" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I22" s="109" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="83"/>
+      <c r="K22" s="81"/>
+    </row>
     <row r="23" spans="1:11" ht="12" customHeight="1"/>
     <row r="24" spans="1:11" ht="12" customHeight="1"/>
     <row r="25" spans="1:11" ht="12" customHeight="1"/>
@@ -3117,8 +3288,11 @@
     <row r="55" ht="12" customHeight="1"/>
     <row r="56" ht="12" customHeight="1"/>
     <row r="57" ht="12" customHeight="1"/>
+    <row r="58" ht="12" customHeight="1"/>
+    <row r="59" ht="12" customHeight="1"/>
+    <row r="60" ht="12" customHeight="1"/>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="30">
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="D16:F16"/>
@@ -3135,8 +3309,6 @@
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:G10"/>
     <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="K9:K10"/>
@@ -3145,6 +3317,12 @@
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
